--- a/output/Data and Chart Outputs/portugal_power_capacity_monthly.xlsx
+++ b/output/Data and Chart Outputs/portugal_power_capacity_monthly.xlsx
@@ -189,12 +189,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$37</f>
+              <f>'Chart'!$A$2:$A$36</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$37</f>
+              <f>'Chart'!$B$2:$B$36</f>
             </numRef>
           </val>
         </ser>
@@ -217,12 +217,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$37</f>
+              <f>'Chart'!$A$2:$A$36</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$C$2:$C$37</f>
+              <f>'Chart'!$C$2:$C$36</f>
             </numRef>
           </val>
         </ser>
@@ -245,12 +245,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$37</f>
+              <f>'Chart'!$A$2:$A$36</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$D$2:$D$37</f>
+              <f>'Chart'!$D$2:$D$36</f>
             </numRef>
           </val>
         </ser>
@@ -273,12 +273,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$37</f>
+              <f>'Chart'!$A$2:$A$36</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$E$2:$E$37</f>
+              <f>'Chart'!$E$2:$E$36</f>
             </numRef>
           </val>
         </ser>
@@ -301,12 +301,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$37</f>
+              <f>'Chart'!$A$2:$A$36</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$F$2:$F$37</f>
+              <f>'Chart'!$F$2:$F$36</f>
             </numRef>
           </val>
         </ser>
@@ -329,12 +329,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$37</f>
+              <f>'Chart'!$A$2:$A$36</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$G$2:$G$37</f>
+              <f>'Chart'!$G$2:$G$36</f>
             </numRef>
           </val>
         </ser>
@@ -368,8 +368,8 @@
         </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
-        <tickLblSkip val="3"/>
-        <tickMarkSkip val="3"/>
+        <tickLblSkip val="2"/>
+        <tickMarkSkip val="2"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -1004,7 +1004,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1072,19 +1072,22 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
-        <v>44440</v>
+        <v>44562</v>
       </c>
       <c r="B3" t="n">
-        <v>7.129</v>
+        <v>4.359</v>
+      </c>
+      <c r="C3" t="n">
+        <v>2.767</v>
       </c>
       <c r="D3" t="n">
-        <v>5.502</v>
+        <v>5.643</v>
       </c>
       <c r="E3" t="n">
-        <v>1.289</v>
+        <v>1.826</v>
       </c>
       <c r="F3" t="n">
-        <v>0.891</v>
+        <v>0.866</v>
       </c>
       <c r="G3" t="n">
         <v>0.034</v>
@@ -1092,22 +1095,22 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
-        <v>44562</v>
+        <v>44927</v>
       </c>
       <c r="B4" t="n">
-        <v>4.359</v>
+        <v>4.479</v>
       </c>
       <c r="C4" t="n">
-        <v>2.767</v>
+        <v>3.649</v>
       </c>
       <c r="D4" t="n">
-        <v>5.643</v>
+        <v>5.731</v>
       </c>
       <c r="E4" t="n">
-        <v>1.826</v>
+        <v>2.69</v>
       </c>
       <c r="F4" t="n">
-        <v>0.866</v>
+        <v>0.862</v>
       </c>
       <c r="G4" t="n">
         <v>0.034</v>
@@ -1115,22 +1118,22 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>44927</v>
+        <v>45292</v>
       </c>
       <c r="B5" t="n">
-        <v>4.479</v>
+        <v>4.477</v>
       </c>
       <c r="C5" t="n">
         <v>3.649</v>
       </c>
       <c r="D5" t="n">
-        <v>5.731</v>
+        <v>5.901</v>
       </c>
       <c r="E5" t="n">
-        <v>2.69</v>
+        <v>3.899</v>
       </c>
       <c r="F5" t="n">
-        <v>0.862</v>
+        <v>0.861</v>
       </c>
       <c r="G5" t="n">
         <v>0.034</v>
@@ -1138,19 +1141,19 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
-        <v>45292</v>
+        <v>45323</v>
       </c>
       <c r="B6" t="n">
-        <v>4.477</v>
+        <v>4.56</v>
       </c>
       <c r="C6" t="n">
-        <v>3.649</v>
+        <v>3.659</v>
       </c>
       <c r="D6" t="n">
-        <v>5.901</v>
+        <v>5.809</v>
       </c>
       <c r="E6" t="n">
-        <v>3.899</v>
+        <v>4.098</v>
       </c>
       <c r="F6" t="n">
         <v>0.861</v>
@@ -1161,7 +1164,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
-        <v>45323</v>
+        <v>45352</v>
       </c>
       <c r="B7" t="n">
         <v>4.56</v>
@@ -1173,7 +1176,7 @@
         <v>5.809</v>
       </c>
       <c r="E7" t="n">
-        <v>4.098</v>
+        <v>4.156</v>
       </c>
       <c r="F7" t="n">
         <v>0.861</v>
@@ -1184,7 +1187,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
-        <v>45352</v>
+        <v>45383</v>
       </c>
       <c r="B8" t="n">
         <v>4.56</v>
@@ -1193,10 +1196,10 @@
         <v>3.659</v>
       </c>
       <c r="D8" t="n">
-        <v>5.809</v>
+        <v>5.888</v>
       </c>
       <c r="E8" t="n">
-        <v>4.156</v>
+        <v>4.277</v>
       </c>
       <c r="F8" t="n">
         <v>0.861</v>
@@ -1207,7 +1210,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>45383</v>
+        <v>45413</v>
       </c>
       <c r="B9" t="n">
         <v>4.56</v>
@@ -1219,10 +1222,10 @@
         <v>5.888</v>
       </c>
       <c r="E9" t="n">
-        <v>4.277</v>
+        <v>4.451</v>
       </c>
       <c r="F9" t="n">
-        <v>0.861</v>
+        <v>0.859</v>
       </c>
       <c r="G9" t="n">
         <v>0.034</v>
@@ -1230,7 +1233,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
-        <v>45413</v>
+        <v>45444</v>
       </c>
       <c r="B10" t="n">
         <v>4.56</v>
@@ -1239,13 +1242,13 @@
         <v>3.659</v>
       </c>
       <c r="D10" t="n">
-        <v>5.888</v>
+        <v>5.901</v>
       </c>
       <c r="E10" t="n">
-        <v>4.451</v>
+        <v>4.592</v>
       </c>
       <c r="F10" t="n">
-        <v>0.859</v>
+        <v>0.858</v>
       </c>
       <c r="G10" t="n">
         <v>0.034</v>
@@ -1253,7 +1256,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>45444</v>
+        <v>45474</v>
       </c>
       <c r="B11" t="n">
         <v>4.56</v>
@@ -1265,10 +1268,10 @@
         <v>5.901</v>
       </c>
       <c r="E11" t="n">
-        <v>4.592</v>
+        <v>4.649</v>
       </c>
       <c r="F11" t="n">
-        <v>0.858</v>
+        <v>0.859</v>
       </c>
       <c r="G11" t="n">
         <v>0.034</v>
@@ -1276,7 +1279,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
-        <v>45474</v>
+        <v>45505</v>
       </c>
       <c r="B12" t="n">
         <v>4.56</v>
@@ -1288,7 +1291,7 @@
         <v>5.901</v>
       </c>
       <c r="E12" t="n">
-        <v>4.649</v>
+        <v>4.881</v>
       </c>
       <c r="F12" t="n">
         <v>0.859</v>
@@ -1299,22 +1302,22 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>45505</v>
+        <v>45536</v>
       </c>
       <c r="B13" t="n">
-        <v>4.56</v>
+        <v>4.64</v>
       </c>
       <c r="C13" t="n">
         <v>3.659</v>
       </c>
       <c r="D13" t="n">
-        <v>5.901</v>
+        <v>5.933</v>
       </c>
       <c r="E13" t="n">
-        <v>4.881</v>
+        <v>4.934</v>
       </c>
       <c r="F13" t="n">
-        <v>0.859</v>
+        <v>0.86</v>
       </c>
       <c r="G13" t="n">
         <v>0.034</v>
@@ -1322,7 +1325,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
-        <v>45536</v>
+        <v>45566</v>
       </c>
       <c r="B14" t="n">
         <v>4.64</v>
@@ -1334,7 +1337,7 @@
         <v>5.933</v>
       </c>
       <c r="E14" t="n">
-        <v>4.934</v>
+        <v>5.005</v>
       </c>
       <c r="F14" t="n">
         <v>0.86</v>
@@ -1345,7 +1348,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>45566</v>
+        <v>45597</v>
       </c>
       <c r="B15" t="n">
         <v>4.64</v>
@@ -1357,7 +1360,7 @@
         <v>5.933</v>
       </c>
       <c r="E15" t="n">
-        <v>5.005</v>
+        <v>5.207</v>
       </c>
       <c r="F15" t="n">
         <v>0.86</v>
@@ -1368,22 +1371,22 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
-        <v>45597</v>
+        <v>45658</v>
       </c>
       <c r="B16" t="n">
-        <v>4.64</v>
+        <v>4.605</v>
       </c>
       <c r="C16" t="n">
-        <v>3.659</v>
+        <v>3.649</v>
       </c>
       <c r="D16" t="n">
-        <v>5.933</v>
+        <v>5.96</v>
       </c>
       <c r="E16" t="n">
-        <v>5.207</v>
+        <v>5.678</v>
       </c>
       <c r="F16" t="n">
-        <v>0.86</v>
+        <v>0.867</v>
       </c>
       <c r="G16" t="n">
         <v>0.034</v>
@@ -1391,22 +1394,22 @@
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>45658</v>
+        <v>45689</v>
       </c>
       <c r="B17" t="n">
-        <v>4.605</v>
+        <v>4.591</v>
       </c>
       <c r="C17" t="n">
-        <v>3.649</v>
+        <v>3.659</v>
       </c>
       <c r="D17" t="n">
-        <v>5.96</v>
+        <v>5.957</v>
       </c>
       <c r="E17" t="n">
-        <v>5.678</v>
+        <v>5.741</v>
       </c>
       <c r="F17" t="n">
-        <v>0.867</v>
+        <v>0.861</v>
       </c>
       <c r="G17" t="n">
         <v>0.034</v>
@@ -1414,7 +1417,7 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
-        <v>45689</v>
+        <v>45717</v>
       </c>
       <c r="B18" t="n">
         <v>4.591</v>
@@ -1426,7 +1429,7 @@
         <v>5.957</v>
       </c>
       <c r="E18" t="n">
-        <v>5.741</v>
+        <v>5.873</v>
       </c>
       <c r="F18" t="n">
         <v>0.861</v>
@@ -1437,7 +1440,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>45717</v>
+        <v>45748</v>
       </c>
       <c r="B19" t="n">
         <v>4.591</v>
@@ -1446,13 +1449,13 @@
         <v>3.659</v>
       </c>
       <c r="D19" t="n">
-        <v>5.957</v>
+        <v>5.963</v>
       </c>
       <c r="E19" t="n">
-        <v>5.873</v>
+        <v>5.956</v>
       </c>
       <c r="F19" t="n">
-        <v>0.861</v>
+        <v>0.867</v>
       </c>
       <c r="G19" t="n">
         <v>0.034</v>
@@ -1460,19 +1463,19 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
-        <v>45748</v>
+        <v>45778</v>
       </c>
       <c r="B20" t="n">
-        <v>4.591</v>
+        <v>4.59</v>
       </c>
       <c r="C20" t="n">
-        <v>3.659</v>
+        <v>3.649</v>
       </c>
       <c r="D20" t="n">
         <v>5.963</v>
       </c>
       <c r="E20" t="n">
-        <v>5.956</v>
+        <v>5.987</v>
       </c>
       <c r="F20" t="n">
         <v>0.867</v>
@@ -1483,10 +1486,10 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>45778</v>
+        <v>45809</v>
       </c>
       <c r="B21" t="n">
-        <v>4.59</v>
+        <v>4.589</v>
       </c>
       <c r="C21" t="n">
         <v>3.649</v>
@@ -1495,7 +1498,7 @@
         <v>5.963</v>
       </c>
       <c r="E21" t="n">
-        <v>5.987</v>
+        <v>6.175</v>
       </c>
       <c r="F21" t="n">
         <v>0.867</v>
@@ -1506,7 +1509,7 @@
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
-        <v>45809</v>
+        <v>45839</v>
       </c>
       <c r="B22" t="n">
         <v>4.589</v>
@@ -1515,10 +1518,10 @@
         <v>3.649</v>
       </c>
       <c r="D22" t="n">
-        <v>5.963</v>
+        <v>5.962</v>
       </c>
       <c r="E22" t="n">
-        <v>6.175</v>
+        <v>6.199</v>
       </c>
       <c r="F22" t="n">
         <v>0.867</v>
@@ -1529,7 +1532,7 @@
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>45839</v>
+        <v>45870</v>
       </c>
       <c r="B23" t="n">
         <v>4.589</v>
@@ -1538,10 +1541,10 @@
         <v>3.649</v>
       </c>
       <c r="D23" t="n">
-        <v>5.962</v>
+        <v>5.965</v>
       </c>
       <c r="E23" t="n">
-        <v>6.199</v>
+        <v>6.302</v>
       </c>
       <c r="F23" t="n">
         <v>0.867</v>
@@ -1552,7 +1555,7 @@
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
-        <v>45870</v>
+        <v>45901</v>
       </c>
       <c r="B24" t="n">
         <v>4.589</v>
@@ -1564,7 +1567,7 @@
         <v>5.965</v>
       </c>
       <c r="E24" t="n">
-        <v>6.302</v>
+        <v>6.32</v>
       </c>
       <c r="F24" t="n">
         <v>0.867</v>
@@ -1575,7 +1578,7 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>45901</v>
+        <v>45931</v>
       </c>
       <c r="B25" t="n">
         <v>4.589</v>
@@ -1587,7 +1590,7 @@
         <v>5.965</v>
       </c>
       <c r="E25" t="n">
-        <v>6.32</v>
+        <v>6.451</v>
       </c>
       <c r="F25" t="n">
         <v>0.867</v>
@@ -1598,7 +1601,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
-        <v>45931</v>
+        <v>45962</v>
       </c>
       <c r="B26" t="n">
         <v>4.589</v>
@@ -1610,7 +1613,7 @@
         <v>5.965</v>
       </c>
       <c r="E26" t="n">
-        <v>6.451</v>
+        <v>6.502</v>
       </c>
       <c r="F26" t="n">
         <v>0.867</v>
@@ -1621,7 +1624,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>45962</v>
+        <v>45992</v>
       </c>
       <c r="B27" t="n">
         <v>4.589</v>
@@ -1633,7 +1636,7 @@
         <v>5.965</v>
       </c>
       <c r="E27" t="n">
-        <v>6.502</v>
+        <v>6.571</v>
       </c>
       <c r="F27" t="n">
         <v>0.867</v>
@@ -1644,22 +1647,22 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="n">
-        <v>45992</v>
+        <v>46023</v>
       </c>
       <c r="B28" t="n">
-        <v>4.589</v>
+        <v>4.606</v>
       </c>
       <c r="C28" t="n">
         <v>3.649</v>
       </c>
       <c r="D28" t="n">
-        <v>5.965</v>
+        <v>5.964</v>
       </c>
       <c r="E28" t="n">
-        <v>6.571</v>
+        <v>6.835</v>
       </c>
       <c r="F28" t="n">
-        <v>0.867</v>
+        <v>0.847</v>
       </c>
       <c r="G28" t="n">
         <v>0.034</v>
@@ -1667,22 +1670,22 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="B29" t="n">
-        <v>4.606</v>
+        <v>4.599</v>
       </c>
       <c r="C29" t="n">
         <v>3.649</v>
       </c>
       <c r="D29" t="n">
-        <v>5.964</v>
+        <v>5.965</v>
       </c>
       <c r="E29" t="n">
-        <v>6.835</v>
+        <v>6.887</v>
       </c>
       <c r="F29" t="n">
-        <v>0.847</v>
+        <v>0.867</v>
       </c>
       <c r="G29" t="n">
         <v>0.034</v>
@@ -1690,7 +1693,7 @@
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="B30" t="n">
         <v>4.599</v>
@@ -1702,7 +1705,7 @@
         <v>5.965</v>
       </c>
       <c r="E30" t="n">
-        <v>6.887</v>
+        <v>6.931</v>
       </c>
       <c r="F30" t="n">
         <v>0.867</v>
@@ -1713,7 +1716,7 @@
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>46082</v>
+        <v>46113</v>
       </c>
       <c r="B31" t="n">
         <v>4.599</v>
@@ -1725,7 +1728,7 @@
         <v>5.965</v>
       </c>
       <c r="E31" t="n">
-        <v>6.931</v>
+        <v>6.961</v>
       </c>
       <c r="F31" t="n">
         <v>0.867</v>
@@ -1736,22 +1739,22 @@
     </row>
     <row r="32">
       <c r="A32" s="3" t="n">
-        <v>46113</v>
+        <v>46143</v>
       </c>
       <c r="B32" t="n">
-        <v>4.599</v>
+        <v>4.606</v>
       </c>
       <c r="C32" t="n">
         <v>3.649</v>
       </c>
       <c r="D32" t="n">
-        <v>5.965</v>
+        <v>6.16</v>
       </c>
       <c r="E32" t="n">
-        <v>6.961</v>
+        <v>7.123</v>
       </c>
       <c r="F32" t="n">
-        <v>0.867</v>
+        <v>0.861</v>
       </c>
       <c r="G32" t="n">
         <v>0.034</v>
@@ -1759,7 +1762,7 @@
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>46143</v>
+        <v>46174</v>
       </c>
       <c r="B33" t="n">
         <v>4.606</v>
@@ -1771,7 +1774,7 @@
         <v>6.16</v>
       </c>
       <c r="E33" t="n">
-        <v>7.123</v>
+        <v>7.215</v>
       </c>
       <c r="F33" t="n">
         <v>0.861</v>
@@ -1782,7 +1785,7 @@
     </row>
     <row r="34">
       <c r="A34" s="3" t="n">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="B34" t="n">
         <v>4.606</v>
@@ -1794,7 +1797,7 @@
         <v>6.16</v>
       </c>
       <c r="E34" t="n">
-        <v>7.215</v>
+        <v>7.243</v>
       </c>
       <c r="F34" t="n">
         <v>0.861</v>
@@ -1805,7 +1808,7 @@
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>46204</v>
+        <v>46235</v>
       </c>
       <c r="B35" t="n">
         <v>4.606</v>
@@ -1814,10 +1817,10 @@
         <v>3.649</v>
       </c>
       <c r="D35" t="n">
-        <v>6.16</v>
+        <v>6.241</v>
       </c>
       <c r="E35" t="n">
-        <v>7.243</v>
+        <v>7.326</v>
       </c>
       <c r="F35" t="n">
         <v>0.861</v>
@@ -1828,7 +1831,7 @@
     </row>
     <row r="36">
       <c r="A36" s="3" t="n">
-        <v>46235</v>
+        <v>46266</v>
       </c>
       <c r="B36" t="n">
         <v>4.606</v>
@@ -1837,38 +1840,15 @@
         <v>3.649</v>
       </c>
       <c r="D36" t="n">
-        <v>6.241</v>
+        <v>6.24</v>
       </c>
       <c r="E36" t="n">
-        <v>7.326</v>
+        <v>7.363</v>
       </c>
       <c r="F36" t="n">
-        <v>0.861</v>
+        <v>0.847</v>
       </c>
       <c r="G36" t="n">
-        <v>0.034</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="n">
-        <v>46266</v>
-      </c>
-      <c r="B37" t="n">
-        <v>4.606</v>
-      </c>
-      <c r="C37" t="n">
-        <v>3.649</v>
-      </c>
-      <c r="D37" t="n">
-        <v>6.24</v>
-      </c>
-      <c r="E37" t="n">
-        <v>7.363</v>
-      </c>
-      <c r="F37" t="n">
-        <v>0.847</v>
-      </c>
-      <c r="G37" t="n">
         <v>0.034</v>
       </c>
     </row>
@@ -2260,7 +2240,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T37"/>
+  <dimension ref="A1:T36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2419,83 +2399,86 @@
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>44440</v>
+        <v>44562</v>
       </c>
       <c r="B3" t="n">
-        <v>7129</v>
+        <v>4359</v>
       </c>
       <c r="D3" t="n">
-        <v>5502</v>
+        <v>5643</v>
       </c>
       <c r="E3" t="n">
-        <v>1289</v>
+        <v>1826</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>891</v>
+        <v>866</v>
       </c>
       <c r="J3" t="n">
         <v>34</v>
       </c>
       <c r="K3" t="n">
-        <v>14846</v>
+        <v>12729</v>
+      </c>
+      <c r="L3" t="n">
+        <v>2767</v>
       </c>
       <c r="N3" t="n">
-        <v>7129</v>
+        <v>7126</v>
       </c>
       <c r="O3" t="n">
-        <v>707</v>
+        <v>679</v>
       </c>
       <c r="P3" t="n">
         <v>89</v>
       </c>
       <c r="Q3" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="R3" t="n">
         <v>34</v>
       </c>
       <c r="S3" t="n">
-        <v>14846</v>
+        <v>15496</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>DGEG report 2021-08</t>
+          <t>DGEG report 2026-08 (31 Dec 2021)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>44562</v>
+        <v>44927</v>
       </c>
       <c r="B4" t="n">
-        <v>4359</v>
+        <v>4479</v>
       </c>
       <c r="D4" t="n">
-        <v>5643</v>
+        <v>5731</v>
       </c>
       <c r="E4" t="n">
-        <v>1826</v>
+        <v>2690</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>866</v>
+        <v>862</v>
       </c>
       <c r="J4" t="n">
         <v>34</v>
       </c>
       <c r="K4" t="n">
-        <v>12729</v>
+        <v>13796</v>
       </c>
       <c r="L4" t="n">
-        <v>2767</v>
+        <v>3649</v>
       </c>
       <c r="N4" t="n">
-        <v>7126</v>
+        <v>8128</v>
       </c>
       <c r="O4" t="n">
         <v>679</v>
@@ -2504,53 +2487,53 @@
         <v>89</v>
       </c>
       <c r="Q4" t="n">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="R4" t="n">
         <v>34</v>
       </c>
       <c r="S4" t="n">
-        <v>15496</v>
+        <v>17445</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>DGEG report 2026-08 (31 Dec 2021)</t>
+          <t>DGEG report 2026-08 (31 Dec 2022)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>44927</v>
+        <v>45292</v>
       </c>
       <c r="B5" t="n">
-        <v>4479</v>
+        <v>4477</v>
       </c>
       <c r="D5" t="n">
-        <v>5731</v>
+        <v>5901</v>
       </c>
       <c r="E5" t="n">
-        <v>2690</v>
+        <v>3899</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="J5" t="n">
         <v>34</v>
       </c>
       <c r="K5" t="n">
-        <v>13796</v>
+        <v>15173</v>
       </c>
       <c r="L5" t="n">
         <v>3649</v>
       </c>
       <c r="N5" t="n">
-        <v>8128</v>
+        <v>8126</v>
       </c>
       <c r="O5" t="n">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="P5" t="n">
         <v>89</v>
@@ -2562,26 +2545,26 @@
         <v>34</v>
       </c>
       <c r="S5" t="n">
-        <v>17445</v>
+        <v>18822</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>DGEG report 2026-08 (31 Dec 2022)</t>
+          <t>DGEG report 2026-08 (31 Dec 2023)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>45292</v>
+        <v>45323</v>
       </c>
       <c r="B6" t="n">
-        <v>4477</v>
+        <v>4560</v>
       </c>
       <c r="D6" t="n">
-        <v>5901</v>
+        <v>5809</v>
       </c>
       <c r="E6" t="n">
-        <v>3899</v>
+        <v>4098</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -2593,38 +2576,38 @@
         <v>34</v>
       </c>
       <c r="K6" t="n">
-        <v>15173</v>
+        <v>15363</v>
       </c>
       <c r="L6" t="n">
-        <v>3649</v>
+        <v>3659</v>
       </c>
       <c r="N6" t="n">
-        <v>8126</v>
+        <v>8219</v>
       </c>
       <c r="O6" t="n">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="P6" t="n">
         <v>89</v>
       </c>
       <c r="Q6" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="R6" t="n">
         <v>34</v>
       </c>
       <c r="S6" t="n">
-        <v>18822</v>
+        <v>19022</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>DGEG report 2026-08 (31 Dec 2023)</t>
+          <t>DGEG report 2024-01</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>45323</v>
+        <v>45352</v>
       </c>
       <c r="B7" t="n">
         <v>4560</v>
@@ -2633,7 +2616,7 @@
         <v>5809</v>
       </c>
       <c r="E7" t="n">
-        <v>4098</v>
+        <v>4156</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -2645,7 +2628,7 @@
         <v>34</v>
       </c>
       <c r="K7" t="n">
-        <v>15363</v>
+        <v>15420</v>
       </c>
       <c r="L7" t="n">
         <v>3659</v>
@@ -2666,26 +2649,26 @@
         <v>34</v>
       </c>
       <c r="S7" t="n">
-        <v>19022</v>
+        <v>19079</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>DGEG report 2024-01</t>
+          <t>DGEG report 2024-02</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>45352</v>
+        <v>45383</v>
       </c>
       <c r="B8" t="n">
         <v>4560</v>
       </c>
       <c r="D8" t="n">
-        <v>5809</v>
+        <v>5888</v>
       </c>
       <c r="E8" t="n">
-        <v>4156</v>
+        <v>4277</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -2697,7 +2680,7 @@
         <v>34</v>
       </c>
       <c r="K8" t="n">
-        <v>15420</v>
+        <v>15621</v>
       </c>
       <c r="L8" t="n">
         <v>3659</v>
@@ -2718,17 +2701,17 @@
         <v>34</v>
       </c>
       <c r="S8" t="n">
-        <v>19079</v>
+        <v>19280</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>DGEG report 2024-02</t>
+          <t>DGEG report 2024-03</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>45383</v>
+        <v>45413</v>
       </c>
       <c r="B9" t="n">
         <v>4560</v>
@@ -2737,19 +2720,19 @@
         <v>5888</v>
       </c>
       <c r="E9" t="n">
-        <v>4277</v>
+        <v>4451</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="J9" t="n">
         <v>34</v>
       </c>
       <c r="K9" t="n">
-        <v>15621</v>
+        <v>15793</v>
       </c>
       <c r="L9" t="n">
         <v>3659</v>
@@ -2758,50 +2741,50 @@
         <v>8219</v>
       </c>
       <c r="O9" t="n">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="P9" t="n">
         <v>89</v>
       </c>
       <c r="Q9" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="R9" t="n">
         <v>34</v>
       </c>
       <c r="S9" t="n">
-        <v>19280</v>
+        <v>19452</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>DGEG report 2024-03</t>
+          <t>DGEG report 2024-04</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>45413</v>
+        <v>45444</v>
       </c>
       <c r="B10" t="n">
         <v>4560</v>
       </c>
       <c r="D10" t="n">
-        <v>5888</v>
+        <v>5901</v>
       </c>
       <c r="E10" t="n">
-        <v>4451</v>
+        <v>4592</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="J10" t="n">
         <v>34</v>
       </c>
       <c r="K10" t="n">
-        <v>15793</v>
+        <v>15946</v>
       </c>
       <c r="L10" t="n">
         <v>3659</v>
@@ -2816,23 +2799,23 @@
         <v>89</v>
       </c>
       <c r="Q10" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="R10" t="n">
         <v>34</v>
       </c>
       <c r="S10" t="n">
-        <v>19452</v>
+        <v>19605</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>DGEG report 2024-04</t>
+          <t>DGEG report 2024-05</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>45444</v>
+        <v>45474</v>
       </c>
       <c r="B11" t="n">
         <v>4560</v>
@@ -2841,19 +2824,19 @@
         <v>5901</v>
       </c>
       <c r="E11" t="n">
-        <v>4592</v>
+        <v>4649</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="J11" t="n">
         <v>34</v>
       </c>
       <c r="K11" t="n">
-        <v>15946</v>
+        <v>16004</v>
       </c>
       <c r="L11" t="n">
         <v>3659</v>
@@ -2868,23 +2851,23 @@
         <v>89</v>
       </c>
       <c r="Q11" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="R11" t="n">
         <v>34</v>
       </c>
       <c r="S11" t="n">
-        <v>19605</v>
+        <v>19663</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>DGEG report 2024-05</t>
+          <t>DGEG report 2024-06</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>45474</v>
+        <v>45505</v>
       </c>
       <c r="B12" t="n">
         <v>4560</v>
@@ -2893,7 +2876,7 @@
         <v>5901</v>
       </c>
       <c r="E12" t="n">
-        <v>4649</v>
+        <v>4881</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -2905,7 +2888,7 @@
         <v>34</v>
       </c>
       <c r="K12" t="n">
-        <v>16004</v>
+        <v>16236</v>
       </c>
       <c r="L12" t="n">
         <v>3659</v>
@@ -2926,44 +2909,44 @@
         <v>34</v>
       </c>
       <c r="S12" t="n">
-        <v>19663</v>
+        <v>19895</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>DGEG report 2024-06</t>
+          <t>DGEG report 2024-07</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>45505</v>
+        <v>45536</v>
       </c>
       <c r="B13" t="n">
-        <v>4560</v>
+        <v>4640</v>
       </c>
       <c r="D13" t="n">
-        <v>5901</v>
+        <v>5933</v>
       </c>
       <c r="E13" t="n">
-        <v>4881</v>
+        <v>4934</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="J13" t="n">
         <v>34</v>
       </c>
       <c r="K13" t="n">
-        <v>16236</v>
+        <v>16402</v>
       </c>
       <c r="L13" t="n">
         <v>3659</v>
       </c>
       <c r="N13" t="n">
-        <v>8219</v>
+        <v>8299</v>
       </c>
       <c r="O13" t="n">
         <v>678</v>
@@ -2972,23 +2955,23 @@
         <v>89</v>
       </c>
       <c r="Q13" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="R13" t="n">
         <v>34</v>
       </c>
       <c r="S13" t="n">
-        <v>19895</v>
+        <v>20061</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>DGEG report 2024-07</t>
+          <t>DGEG report 2024-08</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
-        <v>45536</v>
+        <v>45566</v>
       </c>
       <c r="B14" t="n">
         <v>4640</v>
@@ -2997,7 +2980,7 @@
         <v>5933</v>
       </c>
       <c r="E14" t="n">
-        <v>4934</v>
+        <v>5005</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -3009,7 +2992,7 @@
         <v>34</v>
       </c>
       <c r="K14" t="n">
-        <v>16402</v>
+        <v>16472</v>
       </c>
       <c r="L14" t="n">
         <v>3659</v>
@@ -3030,17 +3013,17 @@
         <v>34</v>
       </c>
       <c r="S14" t="n">
-        <v>20061</v>
+        <v>20131</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>DGEG report 2024-08</t>
+          <t>DGEG report 2024-09</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
-        <v>45566</v>
+        <v>45597</v>
       </c>
       <c r="B15" t="n">
         <v>4640</v>
@@ -3049,7 +3032,7 @@
         <v>5933</v>
       </c>
       <c r="E15" t="n">
-        <v>5005</v>
+        <v>5207</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -3061,7 +3044,7 @@
         <v>34</v>
       </c>
       <c r="K15" t="n">
-        <v>16472</v>
+        <v>16674</v>
       </c>
       <c r="L15" t="n">
         <v>3659</v>
@@ -3082,99 +3065,99 @@
         <v>34</v>
       </c>
       <c r="S15" t="n">
-        <v>20131</v>
+        <v>20333</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>DGEG report 2024-09</t>
+          <t>DGEG report 2024-10</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
-        <v>45597</v>
+        <v>45658</v>
       </c>
       <c r="B16" t="n">
-        <v>4640</v>
+        <v>4605</v>
       </c>
       <c r="D16" t="n">
-        <v>5933</v>
+        <v>5960</v>
       </c>
       <c r="E16" t="n">
-        <v>5207</v>
+        <v>5678</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>860</v>
+        <v>867</v>
       </c>
       <c r="J16" t="n">
         <v>34</v>
       </c>
       <c r="K16" t="n">
-        <v>16674</v>
+        <v>17145</v>
       </c>
       <c r="L16" t="n">
-        <v>3659</v>
+        <v>3649</v>
       </c>
       <c r="N16" t="n">
-        <v>8299</v>
+        <v>8254</v>
       </c>
       <c r="O16" t="n">
-        <v>678</v>
+        <v>684</v>
       </c>
       <c r="P16" t="n">
         <v>89</v>
       </c>
       <c r="Q16" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="R16" t="n">
         <v>34</v>
       </c>
       <c r="S16" t="n">
-        <v>20333</v>
+        <v>20794</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>DGEG report 2024-10</t>
+          <t>DGEG report 2026-08 (31 Dec 2024)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
-        <v>45658</v>
+        <v>45689</v>
       </c>
       <c r="B17" t="n">
-        <v>4605</v>
+        <v>4591</v>
       </c>
       <c r="D17" t="n">
-        <v>5960</v>
+        <v>5957</v>
       </c>
       <c r="E17" t="n">
-        <v>5678</v>
+        <v>5741</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>867</v>
+        <v>861</v>
       </c>
       <c r="J17" t="n">
         <v>34</v>
       </c>
       <c r="K17" t="n">
-        <v>17145</v>
+        <v>17184</v>
       </c>
       <c r="L17" t="n">
-        <v>3649</v>
+        <v>3659</v>
       </c>
       <c r="N17" t="n">
-        <v>8254</v>
+        <v>8250</v>
       </c>
       <c r="O17" t="n">
-        <v>684</v>
+        <v>678</v>
       </c>
       <c r="P17" t="n">
         <v>89</v>
@@ -3186,17 +3169,17 @@
         <v>34</v>
       </c>
       <c r="S17" t="n">
-        <v>20794</v>
+        <v>20843</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>DGEG report 2026-08 (31 Dec 2024)</t>
+          <t>DGEG report 2025-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
-        <v>45689</v>
+        <v>45717</v>
       </c>
       <c r="B18" t="n">
         <v>4591</v>
@@ -3205,7 +3188,7 @@
         <v>5957</v>
       </c>
       <c r="E18" t="n">
-        <v>5741</v>
+        <v>5873</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -3217,7 +3200,7 @@
         <v>34</v>
       </c>
       <c r="K18" t="n">
-        <v>17184</v>
+        <v>17317</v>
       </c>
       <c r="L18" t="n">
         <v>3659</v>
@@ -3238,38 +3221,38 @@
         <v>34</v>
       </c>
       <c r="S18" t="n">
-        <v>20843</v>
+        <v>20976</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>DGEG report 2025-01</t>
+          <t>DGEG report 2025-02</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
-        <v>45717</v>
+        <v>45748</v>
       </c>
       <c r="B19" t="n">
         <v>4591</v>
       </c>
       <c r="D19" t="n">
-        <v>5957</v>
+        <v>5963</v>
       </c>
       <c r="E19" t="n">
-        <v>5873</v>
+        <v>5956</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>861</v>
+        <v>867</v>
       </c>
       <c r="J19" t="n">
         <v>34</v>
       </c>
       <c r="K19" t="n">
-        <v>17317</v>
+        <v>17411</v>
       </c>
       <c r="L19" t="n">
         <v>3659</v>
@@ -3278,7 +3261,7 @@
         <v>8250</v>
       </c>
       <c r="O19" t="n">
-        <v>678</v>
+        <v>684</v>
       </c>
       <c r="P19" t="n">
         <v>89</v>
@@ -3290,26 +3273,26 @@
         <v>34</v>
       </c>
       <c r="S19" t="n">
-        <v>20976</v>
+        <v>21070</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>DGEG report 2025-02</t>
+          <t>DGEG report 2025-03</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
-        <v>45748</v>
+        <v>45778</v>
       </c>
       <c r="B20" t="n">
-        <v>4591</v>
+        <v>4590</v>
       </c>
       <c r="D20" t="n">
         <v>5963</v>
       </c>
       <c r="E20" t="n">
-        <v>5956</v>
+        <v>5987</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -3321,13 +3304,13 @@
         <v>34</v>
       </c>
       <c r="K20" t="n">
-        <v>17411</v>
+        <v>17441</v>
       </c>
       <c r="L20" t="n">
-        <v>3659</v>
+        <v>3649</v>
       </c>
       <c r="N20" t="n">
-        <v>8250</v>
+        <v>8239</v>
       </c>
       <c r="O20" t="n">
         <v>684</v>
@@ -3342,26 +3325,26 @@
         <v>34</v>
       </c>
       <c r="S20" t="n">
-        <v>21070</v>
+        <v>21090</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>DGEG report 2025-03</t>
+          <t>DGEG report 2025-04</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
-        <v>45778</v>
+        <v>45809</v>
       </c>
       <c r="B21" t="n">
-        <v>4590</v>
+        <v>4589</v>
       </c>
       <c r="D21" t="n">
         <v>5963</v>
       </c>
       <c r="E21" t="n">
-        <v>5987</v>
+        <v>6175</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -3373,13 +3356,13 @@
         <v>34</v>
       </c>
       <c r="K21" t="n">
-        <v>17441</v>
+        <v>17628</v>
       </c>
       <c r="L21" t="n">
         <v>3649</v>
       </c>
       <c r="N21" t="n">
-        <v>8239</v>
+        <v>8238</v>
       </c>
       <c r="O21" t="n">
         <v>684</v>
@@ -3394,26 +3377,26 @@
         <v>34</v>
       </c>
       <c r="S21" t="n">
-        <v>21090</v>
+        <v>21277</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>DGEG report 2025-04</t>
+          <t>DGEG report 2025-05</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
-        <v>45809</v>
+        <v>45839</v>
       </c>
       <c r="B22" t="n">
         <v>4589</v>
       </c>
       <c r="D22" t="n">
-        <v>5963</v>
+        <v>5962</v>
       </c>
       <c r="E22" t="n">
-        <v>6175</v>
+        <v>6199</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -3425,7 +3408,7 @@
         <v>34</v>
       </c>
       <c r="K22" t="n">
-        <v>17628</v>
+        <v>17651</v>
       </c>
       <c r="L22" t="n">
         <v>3649</v>
@@ -3446,26 +3429,26 @@
         <v>34</v>
       </c>
       <c r="S22" t="n">
-        <v>21277</v>
+        <v>21300</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>DGEG report 2025-05</t>
+          <t>DGEG report 2025-06</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
-        <v>45839</v>
+        <v>45870</v>
       </c>
       <c r="B23" t="n">
         <v>4589</v>
       </c>
       <c r="D23" t="n">
-        <v>5962</v>
+        <v>5965</v>
       </c>
       <c r="E23" t="n">
-        <v>6199</v>
+        <v>6302</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -3477,7 +3460,7 @@
         <v>34</v>
       </c>
       <c r="K23" t="n">
-        <v>17651</v>
+        <v>17757</v>
       </c>
       <c r="L23" t="n">
         <v>3649</v>
@@ -3498,17 +3481,17 @@
         <v>34</v>
       </c>
       <c r="S23" t="n">
-        <v>21300</v>
+        <v>21406</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>DGEG report 2025-06</t>
+          <t>DGEG report 2025-07</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
-        <v>45870</v>
+        <v>45901</v>
       </c>
       <c r="B24" t="n">
         <v>4589</v>
@@ -3517,7 +3500,7 @@
         <v>5965</v>
       </c>
       <c r="E24" t="n">
-        <v>6302</v>
+        <v>6320</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -3529,7 +3512,7 @@
         <v>34</v>
       </c>
       <c r="K24" t="n">
-        <v>17757</v>
+        <v>17775</v>
       </c>
       <c r="L24" t="n">
         <v>3649</v>
@@ -3550,17 +3533,17 @@
         <v>34</v>
       </c>
       <c r="S24" t="n">
-        <v>21406</v>
+        <v>21424</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>DGEG report 2025-07</t>
+          <t>DGEG report 2025-08</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
-        <v>45901</v>
+        <v>45931</v>
       </c>
       <c r="B25" t="n">
         <v>4589</v>
@@ -3569,7 +3552,7 @@
         <v>5965</v>
       </c>
       <c r="E25" t="n">
-        <v>6320</v>
+        <v>6451</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -3581,7 +3564,7 @@
         <v>34</v>
       </c>
       <c r="K25" t="n">
-        <v>17775</v>
+        <v>17906</v>
       </c>
       <c r="L25" t="n">
         <v>3649</v>
@@ -3602,17 +3585,17 @@
         <v>34</v>
       </c>
       <c r="S25" t="n">
-        <v>21424</v>
+        <v>21555</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>DGEG report 2025-08</t>
+          <t>DGEG report 2025-09</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="n">
-        <v>45931</v>
+        <v>45962</v>
       </c>
       <c r="B26" t="n">
         <v>4589</v>
@@ -3621,7 +3604,7 @@
         <v>5965</v>
       </c>
       <c r="E26" t="n">
-        <v>6451</v>
+        <v>6502</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -3633,7 +3616,7 @@
         <v>34</v>
       </c>
       <c r="K26" t="n">
-        <v>17906</v>
+        <v>17957</v>
       </c>
       <c r="L26" t="n">
         <v>3649</v>
@@ -3654,17 +3637,17 @@
         <v>34</v>
       </c>
       <c r="S26" t="n">
-        <v>21555</v>
+        <v>21606</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>DGEG report 2025-09</t>
+          <t>DGEG report 2025-10</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="n">
-        <v>45962</v>
+        <v>45992</v>
       </c>
       <c r="B27" t="n">
         <v>4589</v>
@@ -3673,7 +3656,7 @@
         <v>5965</v>
       </c>
       <c r="E27" t="n">
-        <v>6502</v>
+        <v>6571</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -3685,7 +3668,7 @@
         <v>34</v>
       </c>
       <c r="K27" t="n">
-        <v>17957</v>
+        <v>18026</v>
       </c>
       <c r="L27" t="n">
         <v>3649</v>
@@ -3706,47 +3689,47 @@
         <v>34</v>
       </c>
       <c r="S27" t="n">
-        <v>21606</v>
+        <v>21675</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>DGEG report 2025-10</t>
+          <t>DGEG report 2025-11</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="n">
-        <v>45992</v>
+        <v>46023</v>
       </c>
       <c r="B28" t="n">
-        <v>4589</v>
+        <v>4606</v>
       </c>
       <c r="D28" t="n">
-        <v>5965</v>
+        <v>5964</v>
       </c>
       <c r="E28" t="n">
-        <v>6571</v>
+        <v>6835</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>867</v>
+        <v>847</v>
       </c>
       <c r="J28" t="n">
         <v>34</v>
       </c>
       <c r="K28" t="n">
-        <v>18026</v>
+        <v>18286</v>
       </c>
       <c r="L28" t="n">
         <v>3649</v>
       </c>
       <c r="N28" t="n">
-        <v>8238</v>
+        <v>8255</v>
       </c>
       <c r="O28" t="n">
-        <v>684</v>
+        <v>664</v>
       </c>
       <c r="P28" t="n">
         <v>89</v>
@@ -3758,47 +3741,47 @@
         <v>34</v>
       </c>
       <c r="S28" t="n">
-        <v>21675</v>
+        <v>21935</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>DGEG report 2025-11</t>
+          <t>DGEG report 2026-08 (31 Dec 2025)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="n">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="B29" t="n">
-        <v>4606</v>
+        <v>4599</v>
       </c>
       <c r="D29" t="n">
-        <v>5964</v>
+        <v>5965</v>
       </c>
       <c r="E29" t="n">
-        <v>6835</v>
+        <v>6887</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>847</v>
+        <v>867</v>
       </c>
       <c r="J29" t="n">
         <v>34</v>
       </c>
       <c r="K29" t="n">
-        <v>18286</v>
+        <v>18352</v>
       </c>
       <c r="L29" t="n">
         <v>3649</v>
       </c>
       <c r="N29" t="n">
-        <v>8255</v>
+        <v>8248</v>
       </c>
       <c r="O29" t="n">
-        <v>664</v>
+        <v>684</v>
       </c>
       <c r="P29" t="n">
         <v>89</v>
@@ -3810,17 +3793,17 @@
         <v>34</v>
       </c>
       <c r="S29" t="n">
-        <v>21935</v>
+        <v>22001</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>DGEG report 2026-08 (31 Dec 2025)</t>
+          <t>DGEG report 2026-01</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="n">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="B30" t="n">
         <v>4599</v>
@@ -3829,7 +3812,7 @@
         <v>5965</v>
       </c>
       <c r="E30" t="n">
-        <v>6887</v>
+        <v>6931</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -3841,7 +3824,7 @@
         <v>34</v>
       </c>
       <c r="K30" t="n">
-        <v>18352</v>
+        <v>18396</v>
       </c>
       <c r="L30" t="n">
         <v>3649</v>
@@ -3862,17 +3845,17 @@
         <v>34</v>
       </c>
       <c r="S30" t="n">
-        <v>22001</v>
+        <v>22045</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>DGEG report 2026-01</t>
+          <t>DGEG report 2026-02</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="n">
-        <v>46082</v>
+        <v>46113</v>
       </c>
       <c r="B31" t="n">
         <v>4599</v>
@@ -3881,7 +3864,7 @@
         <v>5965</v>
       </c>
       <c r="E31" t="n">
-        <v>6931</v>
+        <v>6961</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -3893,7 +3876,7 @@
         <v>34</v>
       </c>
       <c r="K31" t="n">
-        <v>18396</v>
+        <v>18425</v>
       </c>
       <c r="L31" t="n">
         <v>3649</v>
@@ -3914,47 +3897,47 @@
         <v>34</v>
       </c>
       <c r="S31" t="n">
-        <v>22045</v>
+        <v>22074</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>DGEG report 2026-02</t>
+          <t>DGEG report 2026-03</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="n">
-        <v>46113</v>
+        <v>46143</v>
       </c>
       <c r="B32" t="n">
-        <v>4599</v>
+        <v>4606</v>
       </c>
       <c r="D32" t="n">
-        <v>5965</v>
+        <v>6160</v>
       </c>
       <c r="E32" t="n">
-        <v>6961</v>
+        <v>7123</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>867</v>
+        <v>861</v>
       </c>
       <c r="J32" t="n">
         <v>34</v>
       </c>
       <c r="K32" t="n">
-        <v>18425</v>
+        <v>18785</v>
       </c>
       <c r="L32" t="n">
         <v>3649</v>
       </c>
       <c r="N32" t="n">
-        <v>8248</v>
+        <v>8255</v>
       </c>
       <c r="O32" t="n">
-        <v>684</v>
+        <v>678</v>
       </c>
       <c r="P32" t="n">
         <v>89</v>
@@ -3966,17 +3949,17 @@
         <v>34</v>
       </c>
       <c r="S32" t="n">
-        <v>22074</v>
+        <v>22434</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>DGEG report 2026-03</t>
+          <t>DGEG report 2026-04</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="n">
-        <v>46143</v>
+        <v>46174</v>
       </c>
       <c r="B33" t="n">
         <v>4606</v>
@@ -3985,7 +3968,7 @@
         <v>6160</v>
       </c>
       <c r="E33" t="n">
-        <v>7123</v>
+        <v>7215</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -3997,7 +3980,7 @@
         <v>34</v>
       </c>
       <c r="K33" t="n">
-        <v>18785</v>
+        <v>18877</v>
       </c>
       <c r="L33" t="n">
         <v>3649</v>
@@ -4018,17 +4001,17 @@
         <v>34</v>
       </c>
       <c r="S33" t="n">
-        <v>22434</v>
+        <v>22526</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>DGEG report 2026-04</t>
+          <t>DGEG report 2026-05</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="n">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="B34" t="n">
         <v>4606</v>
@@ -4037,7 +4020,7 @@
         <v>6160</v>
       </c>
       <c r="E34" t="n">
-        <v>7215</v>
+        <v>7243</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -4049,7 +4032,7 @@
         <v>34</v>
       </c>
       <c r="K34" t="n">
-        <v>18877</v>
+        <v>18905</v>
       </c>
       <c r="L34" t="n">
         <v>3649</v>
@@ -4070,26 +4053,26 @@
         <v>34</v>
       </c>
       <c r="S34" t="n">
-        <v>22526</v>
+        <v>22554</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>DGEG report 2026-05</t>
+          <t>DGEG report 2026-06</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="n">
-        <v>46204</v>
+        <v>46235</v>
       </c>
       <c r="B35" t="n">
         <v>4606</v>
       </c>
       <c r="D35" t="n">
-        <v>6160</v>
+        <v>6241</v>
       </c>
       <c r="E35" t="n">
-        <v>7243</v>
+        <v>7326</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -4101,7 +4084,7 @@
         <v>34</v>
       </c>
       <c r="K35" t="n">
-        <v>18905</v>
+        <v>19069</v>
       </c>
       <c r="L35" t="n">
         <v>3649</v>
@@ -4122,38 +4105,38 @@
         <v>34</v>
       </c>
       <c r="S35" t="n">
-        <v>22554</v>
+        <v>22718</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>DGEG report 2026-06</t>
+          <t>DGEG report 2026-07</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="n">
-        <v>46235</v>
+        <v>46266</v>
       </c>
       <c r="B36" t="n">
         <v>4606</v>
       </c>
       <c r="D36" t="n">
-        <v>6241</v>
+        <v>6240</v>
       </c>
       <c r="E36" t="n">
-        <v>7326</v>
+        <v>7363</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>861</v>
+        <v>847</v>
       </c>
       <c r="J36" t="n">
         <v>34</v>
       </c>
       <c r="K36" t="n">
-        <v>19069</v>
+        <v>19090</v>
       </c>
       <c r="L36" t="n">
         <v>3649</v>
@@ -4162,7 +4145,7 @@
         <v>8255</v>
       </c>
       <c r="O36" t="n">
-        <v>678</v>
+        <v>664</v>
       </c>
       <c r="P36" t="n">
         <v>89</v>
@@ -4174,61 +4157,9 @@
         <v>34</v>
       </c>
       <c r="S36" t="n">
-        <v>22718</v>
+        <v>22739</v>
       </c>
       <c r="T36" t="inlineStr">
-        <is>
-          <t>DGEG report 2026-07</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="4" t="n">
-        <v>46266</v>
-      </c>
-      <c r="B37" t="n">
-        <v>4606</v>
-      </c>
-      <c r="D37" t="n">
-        <v>6240</v>
-      </c>
-      <c r="E37" t="n">
-        <v>7363</v>
-      </c>
-      <c r="G37" t="n">
-        <v>0</v>
-      </c>
-      <c r="I37" t="n">
-        <v>847</v>
-      </c>
-      <c r="J37" t="n">
-        <v>34</v>
-      </c>
-      <c r="K37" t="n">
-        <v>19090</v>
-      </c>
-      <c r="L37" t="n">
-        <v>3649</v>
-      </c>
-      <c r="N37" t="n">
-        <v>8255</v>
-      </c>
-      <c r="O37" t="n">
-        <v>664</v>
-      </c>
-      <c r="P37" t="n">
-        <v>89</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>94</v>
-      </c>
-      <c r="R37" t="n">
-        <v>34</v>
-      </c>
-      <c r="S37" t="n">
-        <v>22739</v>
-      </c>
-      <c r="T37" t="inlineStr">
         <is>
           <t>DGEG report 2026-08</t>
         </is>
@@ -4979,44 +4910,24 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>DGEG 2020-12</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-10-12 04:47 UTC</t>
+          <t>DGEG 2021-08</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.dgeg.gov.pt/media/zazjmhkh/dgeg-arr-2020-12.pdf</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>1857961b757e047af138efeec32ba18448a1c04841c65592d234760ba99b1589</t>
+          <t>https://www.dgeg.gov.pt/media/1s2i0vpx/dgeg-arr-2021-08.pdf</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DGEG 2021-08</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-10-12 04:47 UTC</t>
+          <t>DGEG 2020-12</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.dgeg.gov.pt/media/1s2i0vpx/dgeg-arr-2021-08.pdf</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>0cf0741bb51aa3bc2443f0cad74e0ddb6f82637c63e84f98b95a83baee5a575c</t>
+          <t>https://www.dgeg.gov.pt/media/zazjmhkh/dgeg-arr-2020-12.pdf</t>
         </is>
       </c>
     </row>
@@ -5026,19 +4937,9 @@
           <t>DGEG 2021-12</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-10-12 04:47 UTC</t>
-        </is>
-      </c>
       <c r="C4" t="inlineStr">
         <is>
           <t>https://www.dgeg.gov.pt/media/5fjpfuk1/dgeg-arr-2021-12_v2.pdf</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>29592629cfa25a75cd9295a87793f70248e03a0ebf42827a16ac41696ac80443</t>
         </is>
       </c>
     </row>
@@ -5048,19 +4949,9 @@
           <t>DGEG 2022-12</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-10-12 04:47 UTC</t>
-        </is>
-      </c>
       <c r="C5" t="inlineStr">
         <is>
           <t>https://www.dgeg.gov.pt/media/cjnfkck0/dgeg-arr-2022-12-v2.pdf</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>c0ef4c5719d0315882576af556b85f25e6fe79b4820c0b097c0d8faf720c9330</t>
         </is>
       </c>
     </row>
@@ -5070,19 +4961,9 @@
           <t>DGEG 2023-12</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-10-12 04:47 UTC</t>
-        </is>
-      </c>
       <c r="C6" t="inlineStr">
         <is>
           <t>https://www.dgeg.gov.pt/media/amioxiec/dgeg-arr-2023-12.pdf</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>9343464158bd4551a22bac6d108c8ffe8208262cc444b3041681facc9f3a705e</t>
         </is>
       </c>
     </row>
@@ -5092,19 +4973,9 @@
           <t>DGEG 2024-01</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-10-12 04:47 UTC</t>
-        </is>
-      </c>
       <c r="C7" t="inlineStr">
         <is>
           <t>https://www.dgeg.gov.pt/media/tmfl1tla/renovaveis-202401.pdf</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>154cf8fc93e14fbc6fb82ca6cdf429770bffdebe32bdcf6d812e66e8e36fb80c</t>
         </is>
       </c>
     </row>
@@ -5114,19 +4985,9 @@
           <t>DGEG 2024-02</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-10-12 04:47 UTC</t>
-        </is>
-      </c>
       <c r="C8" t="inlineStr">
         <is>
           <t>https://www.dgeg.gov.pt/media/mdmivv3u/dgeg-arr-2024-02.pdf</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>a21f54c62f084f234fb2f9862fcb989e37293da0ed52c25cd59acee2d239cdcf</t>
         </is>
       </c>
     </row>
@@ -5136,19 +4997,9 @@
           <t>DGEG 2024-03</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-10-12 04:47 UTC</t>
-        </is>
-      </c>
       <c r="C9" t="inlineStr">
         <is>
           <t>https://www.dgeg.gov.pt/media/5w2mx33b/dgeg-arr-2024-03.pdf</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>c3378aeb479b43ce0cc450db0dc2038da4e465de5d70437981d7ac65acbd5d0e</t>
         </is>
       </c>
     </row>
@@ -5158,19 +5009,9 @@
           <t>DGEG 2024-04</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2026-10-12 04:47 UTC</t>
-        </is>
-      </c>
       <c r="C10" t="inlineStr">
         <is>
           <t>https://www.dgeg.gov.pt/media/um5jqbue/dgeg-arr-2024-04.pdf</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>5bda5b0bd4936b9e76600d11d03f2b8ac6c5fd703ce5493ed88bd43d792a71c0</t>
         </is>
       </c>
     </row>
@@ -5180,19 +5021,9 @@
           <t>DGEG 2024-05</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2026-10-12 04:47 UTC</t>
-        </is>
-      </c>
       <c r="C11" t="inlineStr">
         <is>
           <t>https://www.dgeg.gov.pt/media/qelpruhg/dgeg-arr-2024-05.pdf</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>ff4b805b559ab5a9911862446a0da508e10a410261bc36691fbddadbafce8c82</t>
         </is>
       </c>
     </row>
@@ -5202,19 +5033,9 @@
           <t>DGEG 2024-06</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2026-10-12 04:47 UTC</t>
-        </is>
-      </c>
       <c r="C12" t="inlineStr">
         <is>
           <t>https://www.dgeg.gov.pt/media/4pdljtkr/dgeg-arr-2024-06.pdf</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>904dbbd7a6b87d7f7894eea4fb6ec91251d3ae927efcfe44d46169c69ab233dc</t>
         </is>
       </c>
     </row>
@@ -5224,19 +5045,9 @@
           <t>DGEG 2024-07</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2026-10-12 04:47 UTC</t>
-        </is>
-      </c>
       <c r="C13" t="inlineStr">
         <is>
           <t>https://www.dgeg.gov.pt/media/ruapg153/dgeg-arr-2024-07.pdf</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>1807bd7ac7ecb5edce4b1862bf590b8e883e1f02ca0b6d89e1abf3bb97277766</t>
         </is>
       </c>
     </row>
@@ -5246,19 +5057,9 @@
           <t>DGEG 2024-08</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2026-10-12 04:47 UTC</t>
-        </is>
-      </c>
       <c r="C14" t="inlineStr">
         <is>
           <t>https://www.dgeg.gov.pt/media/qdidnmxu/dgeg-arr-2024-08.pdf</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>32f2cb060729c402b255f1b6f67b34d1854115f50b4672f02d7856dbeea1f36f</t>
         </is>
       </c>
     </row>
@@ -5268,19 +5069,9 @@
           <t>DGEG 2024-09</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2026-10-12 04:47 UTC</t>
-        </is>
-      </c>
       <c r="C15" t="inlineStr">
         <is>
           <t>https://www.dgeg.gov.pt/media/e5vpyh3g/dgeg-arr-2024-09.pdf</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>ae9bd7f1427bc6b44ea80c2e365f3c594dd9f1fbd25fe8c8f115bc1acf4f6d82</t>
         </is>
       </c>
     </row>
@@ -5290,19 +5081,9 @@
           <t>DGEG 2024-10</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2026-10-12 04:47 UTC</t>
-        </is>
-      </c>
       <c r="C16" t="inlineStr">
         <is>
           <t>https://www.dgeg.gov.pt/media/krcns4st/dgeg-arr-2024-10.pdf</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>2b9f907fb1facff0da1ddd1de03869bb0c6912d3e772c9d276863192c7f481b9</t>
         </is>
       </c>
     </row>
@@ -5312,19 +5093,9 @@
           <t>DGEG 2024-12</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2026-10-12 04:47 UTC</t>
-        </is>
-      </c>
       <c r="C17" t="inlineStr">
         <is>
           <t>https://www.dgeg.gov.pt/media/e14basma/dgeg-arr-2024-12-v1.pdf</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>b85ddde44c898b7f8a511b6670081c0d229853c2d02bb60828a32b92772227d0</t>
         </is>
       </c>
     </row>
@@ -5334,19 +5105,9 @@
           <t>DGEG 2025-01</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2026-10-12 04:47 UTC</t>
-        </is>
-      </c>
       <c r="C18" t="inlineStr">
         <is>
           <t>https://www.dgeg.gov.pt/media/lfmhngdq/dgeg-arr-2025-01.pdf</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>1d1edc9113200d03de1ba8b9238dadccaf0a3df510e737ef48ef7696b19a886e</t>
         </is>
       </c>
     </row>
@@ -5356,19 +5117,9 @@
           <t>DGEG 2025-02</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2026-10-12 04:47 UTC</t>
-        </is>
-      </c>
       <c r="C19" t="inlineStr">
         <is>
           <t>https://www.dgeg.gov.pt/media/upclbs5j/dgeg-arr-2025-02.pdf</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>0a5c4a6d64258578d52ced14da88521f60bd0bf35fbdf387ed107759e16d5cad</t>
         </is>
       </c>
     </row>
@@ -5378,19 +5129,9 @@
           <t>DGEG 2025-03</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2026-10-12 04:47 UTC</t>
-        </is>
-      </c>
       <c r="C20" t="inlineStr">
         <is>
           <t>https://www.dgeg.gov.pt/media/abmpkzsu/dgeg-arr-2025-03.pdf</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>ba4ca526064772f59a6d58574b93c0ce7df8e9f5ebfa7c6fc012d961b838a1b1</t>
         </is>
       </c>
     </row>
@@ -5400,19 +5141,9 @@
           <t>DGEG 2025-04</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2026-10-12 04:47 UTC</t>
-        </is>
-      </c>
       <c r="C21" t="inlineStr">
         <is>
           <t>https://www.dgeg.gov.pt/media/kluh33x2/dgeg-arr-2025-04.pdf</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>c7d6384a005f0cc1b4834f035c65a7846bae84868b947489683e3ab37df6daf8</t>
         </is>
       </c>
     </row>
@@ -5422,19 +5153,9 @@
           <t>DGEG 2025-05</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2026-10-12 04:47 UTC</t>
-        </is>
-      </c>
       <c r="C22" t="inlineStr">
         <is>
           <t>https://www.dgeg.gov.pt/media/uqtcinqo/dgeg-arr-2025-05.pdf</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>2447b5913750476d6223a110bf3d1239ae503871d7cc638c9091ac08ef1937bf</t>
         </is>
       </c>
     </row>
@@ -5444,19 +5165,9 @@
           <t>DGEG 2025-06</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2026-10-12 04:47 UTC</t>
-        </is>
-      </c>
       <c r="C23" t="inlineStr">
         <is>
           <t>https://www.dgeg.gov.pt/media/aqmpm3cf/dgeg-arr-2025-06.pdf</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>a8dbc8a6dfef46f9d9b5e69fad74456a7e517365772f43a189dcb68f552f1ebe</t>
         </is>
       </c>
     </row>
@@ -5466,19 +5177,9 @@
           <t>DGEG 2025-07</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2026-10-12 04:47 UTC</t>
-        </is>
-      </c>
       <c r="C24" t="inlineStr">
         <is>
           <t>https://www.dgeg.gov.pt/media/sjiphcim/dgeg-arr-2025-07.pdf</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>f15f4ef1203c62ccf7a28def63652b16a8b62b765afabfb5a902350db88fedef</t>
         </is>
       </c>
     </row>
@@ -5488,19 +5189,9 @@
           <t>DGEG 2025-08</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2026-10-12 04:47 UTC</t>
-        </is>
-      </c>
       <c r="C25" t="inlineStr">
         <is>
           <t>https://www.dgeg.gov.pt/media/1dyj1wo1/dgeg-arr-2025-08.pdf</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>b3a2c8fc77568495ed91dda0da2a62aee0992786cc88ddf4eb4b085036529d21</t>
         </is>
       </c>
     </row>
@@ -5510,19 +5201,9 @@
           <t>DGEG 2025-09</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2026-10-12 04:47 UTC</t>
-        </is>
-      </c>
       <c r="C26" t="inlineStr">
         <is>
           <t>https://www.dgeg.gov.pt/media/v0qnipij/dgeg-arr-2025-09.pdf</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>96b6bc19d522b56c511d05d34d20ddc0dcea8610d6d8689f3b19c36b0c46e594</t>
         </is>
       </c>
     </row>
@@ -5532,19 +5213,9 @@
           <t>DGEG 2025-10</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2026-10-12 04:47 UTC</t>
-        </is>
-      </c>
       <c r="C27" t="inlineStr">
         <is>
           <t>https://www.dgeg.gov.pt/media/a5nne0vg/dgeg-arr-2025-10.pdf</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>1ac46355e8174120758e1397d663f682bd10d37f14cb7c13ac6b7e36c6fa043f</t>
         </is>
       </c>
     </row>
@@ -5554,19 +5225,9 @@
           <t>DGEG 2025-11</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2026-10-12 04:47 UTC</t>
-        </is>
-      </c>
       <c r="C28" t="inlineStr">
         <is>
           <t>https://www.dgeg.gov.pt/media/zm3hyme1/dgeg-arr-2025-11.pdf</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>7a3486814a82a921e03760637d8c914d54525b2b8fd1ab0b992643bc0916f80b</t>
         </is>
       </c>
     </row>
@@ -5576,19 +5237,9 @@
           <t>DGEG 2025-12</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2026-10-12 04:47 UTC</t>
-        </is>
-      </c>
       <c r="C29" t="inlineStr">
         <is>
           <t>https://www.dgeg.gov.pt/media/qybp4lbt/dgeg-arr-2025-12.pdf</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>a681b90a7f5471301012a98261fd608901b067fc9e717c01034e8ad55d0562bd</t>
         </is>
       </c>
     </row>
@@ -5598,19 +5249,9 @@
           <t>DGEG 2026-01</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>2026-10-12 04:47 UTC</t>
-        </is>
-      </c>
       <c r="C30" t="inlineStr">
         <is>
           <t>https://www.dgeg.gov.pt/media/eepfhxw1/dgeg-arr-2026-01.pdf</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>afe8c061334a3e256165cd9dc645a90f4e9c8c893a92dd34cda6502fa1ea1e7e</t>
         </is>
       </c>
     </row>
@@ -5620,19 +5261,9 @@
           <t>DGEG 2026-02</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>2026-10-12 04:47 UTC</t>
-        </is>
-      </c>
       <c r="C31" t="inlineStr">
         <is>
           <t>https://www.dgeg.gov.pt/media/ge2hwoxe/dgeg-arr-2026-02.pdf</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>25d4cd74f8072f5169e59896c37999977894bea3f86fcb735ad1af19753fd75d</t>
         </is>
       </c>
     </row>
@@ -5642,19 +5273,9 @@
           <t>DGEG 2026-03</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>2026-10-12 04:47 UTC</t>
-        </is>
-      </c>
       <c r="C32" t="inlineStr">
         <is>
           <t>https://www.dgeg.gov.pt/media/v2llqxp5/dgeg-arr-2026-03.pdf</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>ef11fb8fab997dcd7fdb88f79c0b0622a51340cf3edf762cfbb7c10a0df3a8fa</t>
         </is>
       </c>
     </row>
@@ -5664,19 +5285,9 @@
           <t>DGEG 2026-04</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>2026-10-12 04:47 UTC</t>
-        </is>
-      </c>
       <c r="C33" t="inlineStr">
         <is>
           <t>https://www.dgeg.gov.pt/media/vukgx0vs/dgeg-arr-2026-04.pdf</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>5ada42115f4245b89175a9c71a97b18c9861a241b9c2b2650fc05b9855d5adbf</t>
         </is>
       </c>
     </row>
@@ -5686,19 +5297,9 @@
           <t>DGEG 2026-05</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>2026-10-12 04:47 UTC</t>
-        </is>
-      </c>
       <c r="C34" t="inlineStr">
         <is>
           <t>https://www.dgeg.gov.pt/media/inqojgad/dgeg-arr-2026-05.pdf</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>55f2a3470cc79f8586dea4e5ed6840799a8b0ff2e9a464c806fd09b27a91e16d</t>
         </is>
       </c>
     </row>
@@ -5708,19 +5309,9 @@
           <t>DGEG 2026-06</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>2026-10-12 04:47 UTC</t>
-        </is>
-      </c>
       <c r="C35" t="inlineStr">
         <is>
           <t>https://www.dgeg.gov.pt/media/wkklkfxm/dgeg-arr-2026-06.pdf</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>a192216c2542d815e07b8926cbb3f4ea6e51328541c94b9572f4782196787e0e</t>
         </is>
       </c>
     </row>
@@ -5732,7 +5323,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-12 04:47 UTC</t>
+          <t>2026-10-12 04:52 UTC</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -5754,7 +5345,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-12 04:47 UTC</t>
+          <t>2026-10-12 04:52 UTC</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">

--- a/output/Data and Chart Outputs/portugal_power_capacity_monthly.xlsx
+++ b/output/Data and Chart Outputs/portugal_power_capacity_monthly.xlsx
@@ -5323,7 +5323,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-12 04:52 UTC</t>
+          <t>2026-10-12 04:54 UTC</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -5345,7 +5345,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-12 04:52 UTC</t>
+          <t>2026-10-12 04:54 UTC</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">

--- a/output/Data and Chart Outputs/portugal_power_capacity_monthly.xlsx
+++ b/output/Data and Chart Outputs/portugal_power_capacity_monthly.xlsx
@@ -5323,7 +5323,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-12 04:54 UTC</t>
+          <t>2026-10-28 01:13 UTC</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -5345,7 +5345,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-12 04:54 UTC</t>
+          <t>2026-10-28 01:13 UTC</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
